--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{59579A27-F95B-4FE7-A975-F4939DBD3575}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{09653C62-4CA3-4213-9539-CB60268A1635}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -306,56 +306,56 @@
     <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -757,15 +757,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -793,19 +793,19 @@
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -828,11 +828,11 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" s="5" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -842,36 +842,36 @@
         <v>1</v>
       </c>
       <c r="C4" s="27"/>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="13">
+      <c r="B5" s="28">
         <v>45887</v>
       </c>
-      <c r="C5" s="13"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="11">
         <f>SUM(C12:I12)</f>
-        <v>0.23611111111111108</v>
+        <v>0.27083333333333326</v>
       </c>
       <c r="E5" s="12">
         <f>SUM(C21:I21)</f>
@@ -895,7 +895,7 @@
       </c>
       <c r="J5" s="12">
         <f>SUM(D5:I5)</f>
-        <v>0.23611111111111108</v>
+        <v>0.27083333333333326</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -908,172 +908,172 @@
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="18">
+      <c r="B7" s="25">
         <v>1</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="15">
         <f>B5</f>
         <v>45887</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="15">
         <f>C7+1</f>
         <v>45888</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="15">
         <f t="shared" ref="E7:I7" si="0">D7+1</f>
         <v>45889</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="15">
         <f t="shared" si="0"/>
         <v>45890</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="15">
         <f t="shared" si="0"/>
         <v>45891</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="15">
         <f t="shared" si="0"/>
         <v>45892</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
         <v>45893</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="20">
+      <c r="B8" s="25"/>
+      <c r="C8" s="16">
         <f>B5</f>
         <v>45887</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="16">
         <f>B5+1</f>
         <v>45888</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <f>B5+2</f>
         <v>45889</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="16">
         <f>B5+3</f>
         <v>45890</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="16">
         <f>B5+4</f>
         <v>45891</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="16">
         <f>B5+5</f>
         <v>45892</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="16">
         <f>B5+6</f>
         <v>45893</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="18">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="22">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
+      <c r="C10" s="18">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="19">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="17"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="21">
         <f>C10-C9-C11</f>
-        <v>0.23611111111111108</v>
-      </c>
-      <c r="D12" s="25">
+        <v>0.27083333333333326</v>
+      </c>
+      <c r="D12" s="21">
         <f t="shared" ref="D12:I12" si="1">D10-D9-D11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:32" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C15" s="10"/>
@@ -1085,791 +1085,791 @@
       <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18">
+      <c r="B16" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="15">
         <f>C17</f>
         <v>45894</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="15">
         <f>C16+1</f>
         <v>45895</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="15">
         <f t="shared" ref="E16:I16" si="2">D16+1</f>
         <v>45896</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="15">
         <f t="shared" si="2"/>
         <v>45897</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="15">
         <f t="shared" si="2"/>
         <v>45898</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="15">
         <f t="shared" si="2"/>
         <v>45899</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="15">
         <f t="shared" si="2"/>
         <v>45900</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="18"/>
-      <c r="C17" s="20">
+      <c r="B17" s="25"/>
+      <c r="C17" s="16">
         <f>I8+1</f>
         <v>45894</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="16">
         <f>I8+2</f>
         <v>45895</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="16">
         <f>I8+3</f>
         <v>45896</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="16">
         <f>I8+4</f>
         <v>45897</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="16">
         <f>I8+5</f>
         <v>45898</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="16">
         <f>I8+6</f>
         <v>45899</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="16">
         <f>I8+7</f>
         <v>45900</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
     </row>
     <row r="19" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="17"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="14"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="21">
         <f>C19-C18-C20</f>
         <v>0</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="21">
         <f>D19-D18-D20</f>
         <v>0</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="21">
         <f t="shared" ref="E21:I21" si="3">E19-E18-E20</f>
         <v>0</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="B23" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="2:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="18">
+      <c r="B25" s="25">
         <v>3</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="15">
         <f>C26</f>
         <v>45901</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="15">
         <f>C25+1</f>
         <v>45902</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="15">
         <f t="shared" ref="E25" si="4">D25+1</f>
         <v>45903</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="15">
         <f t="shared" ref="F25" si="5">E25+1</f>
         <v>45904</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="15">
         <f t="shared" ref="G25" si="6">F25+1</f>
         <v>45905</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="15">
         <f t="shared" ref="H25" si="7">G25+1</f>
         <v>45906</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="15">
         <f t="shared" ref="I25" si="8">H25+1</f>
         <v>45907</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="18"/>
-      <c r="C26" s="20">
+      <c r="B26" s="25"/>
+      <c r="C26" s="16">
         <f>I17+1</f>
         <v>45901</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="16">
         <f>I17+2</f>
         <v>45902</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="16">
         <f>I17+3</f>
         <v>45903</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="16">
         <f>I17+4</f>
         <v>45904</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="16">
         <f>I17+5</f>
         <v>45905</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="16">
         <f>I17+6</f>
         <v>45906</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="16">
         <f>I17+7</f>
         <v>45907</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" spans="2:10" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" spans="2:10" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" spans="2:10" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="21">
         <f>C28-C27-C29</f>
         <v>0</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="21">
         <f>D28-D27-D29</f>
         <v>0</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="21">
         <f t="shared" ref="E30" si="9">E28-E27-E29</f>
         <v>0</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="21">
         <f t="shared" ref="F30" si="10">F28-F27-F29</f>
         <v>0</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="21">
         <f t="shared" ref="G30" si="11">G28-G27-G29</f>
         <v>0</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="21">
         <f t="shared" ref="H30" si="12">H28-H27-H29</f>
         <v>0</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="21">
         <f t="shared" ref="I30" si="13">I28-I27-I29</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="2:10" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
+      <c r="B32" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="18">
+      <c r="B34" s="25">
         <v>4</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="15">
         <f>C35</f>
         <v>45908</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="15">
         <f>C34+1</f>
         <v>45909</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="15">
         <f t="shared" ref="E34" si="14">D34+1</f>
         <v>45910</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="15">
         <f t="shared" ref="F34" si="15">E34+1</f>
         <v>45911</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="15">
         <f t="shared" ref="G34" si="16">F34+1</f>
         <v>45912</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="15">
         <f t="shared" ref="H34" si="17">G34+1</f>
         <v>45913</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="15">
         <f t="shared" ref="I34" si="18">H34+1</f>
         <v>45914</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="18"/>
-      <c r="C35" s="20">
+      <c r="B35" s="25"/>
+      <c r="C35" s="16">
         <f>I26+1</f>
         <v>45908</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="16">
         <f>I26+2</f>
         <v>45909</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="16">
         <f>I26+3</f>
         <v>45910</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="16">
         <f>I26+4</f>
         <v>45911</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="16">
         <f>I26+5</f>
         <v>45912</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="16">
         <f>I26+6</f>
         <v>45913</v>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="16">
         <f>I26+7</f>
         <v>45914</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
     </row>
     <row r="37" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
     </row>
     <row r="38" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
     </row>
     <row r="39" spans="2:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="21">
         <f>C37-C36-C38</f>
         <v>0</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="21">
         <f>D37-D36-D38</f>
         <v>0</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="21">
         <f t="shared" ref="E39" si="19">E37-E36-E38</f>
         <v>0</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="21">
         <f t="shared" ref="F39" si="20">F37-F36-F38</f>
         <v>0</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="21">
         <f t="shared" ref="G39" si="21">G37-G36-G38</f>
         <v>0</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="21">
         <f t="shared" ref="H39" si="22">H37-H36-H38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="21">
         <f t="shared" ref="I39" si="23">I37-I36-I38</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
     </row>
     <row r="41" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
+      <c r="B41" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
     </row>
     <row r="43" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="18">
+      <c r="B43" s="25">
         <v>5</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="15">
         <f>C44</f>
         <v>45915</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="15">
         <f>C43+1</f>
         <v>45916</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="15">
         <f t="shared" ref="E43" si="24">D43+1</f>
         <v>45917</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="15">
         <f t="shared" ref="F43" si="25">E43+1</f>
         <v>45918</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="15">
         <f t="shared" ref="G43" si="26">F43+1</f>
         <v>45919</v>
       </c>
-      <c r="H43" s="19">
+      <c r="H43" s="15">
         <f t="shared" ref="H43" si="27">G43+1</f>
         <v>45920</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="15">
         <f t="shared" ref="I43" si="28">H43+1</f>
         <v>45921</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="18"/>
-      <c r="C44" s="20">
+      <c r="B44" s="25"/>
+      <c r="C44" s="16">
         <f>I35+1</f>
         <v>45915</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="16">
         <f>I35+2</f>
         <v>45916</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="16">
         <f>I35+3</f>
         <v>45917</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="16">
         <f>I35+4</f>
         <v>45918</v>
       </c>
-      <c r="G44" s="20">
+      <c r="G44" s="16">
         <f>I35+5</f>
         <v>45919</v>
       </c>
-      <c r="H44" s="20">
+      <c r="H44" s="16">
         <f>I35+6</f>
         <v>45920</v>
       </c>
-      <c r="I44" s="20">
+      <c r="I44" s="16">
         <f>I35+7</f>
         <v>45921</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
     </row>
     <row r="46" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
     </row>
     <row r="47" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
     </row>
     <row r="48" spans="2:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="21">
         <f>C46-C45-C47</f>
         <v>0</v>
       </c>
-      <c r="D48" s="25">
+      <c r="D48" s="21">
         <f>D46-D45-D47</f>
         <v>0</v>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="21">
         <f t="shared" ref="E48" si="29">E46-E45-E47</f>
         <v>0</v>
       </c>
-      <c r="F48" s="25">
+      <c r="F48" s="21">
         <f t="shared" ref="F48" si="30">F46-F45-F47</f>
         <v>0</v>
       </c>
-      <c r="G48" s="25">
+      <c r="G48" s="21">
         <f t="shared" ref="G48" si="31">G46-G45-G47</f>
         <v>0</v>
       </c>
-      <c r="H48" s="25">
+      <c r="H48" s="21">
         <f t="shared" ref="H48" si="32">H46-H45-H47</f>
         <v>0</v>
       </c>
-      <c r="I48" s="25">
+      <c r="I48" s="21">
         <f t="shared" ref="I48" si="33">I46-I45-I47</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
     </row>
     <row r="50" spans="2:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
+      <c r="B50" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
     </row>
     <row r="52" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="18">
+      <c r="B52" s="25">
         <v>6</v>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="15">
         <f>C53</f>
         <v>45922</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="15">
         <f>C52+1</f>
         <v>45923</v>
       </c>
-      <c r="E52" s="19">
+      <c r="E52" s="15">
         <f t="shared" ref="E52" si="34">D52+1</f>
         <v>45924</v>
       </c>
-      <c r="F52" s="19">
+      <c r="F52" s="15">
         <f t="shared" ref="F52" si="35">E52+1</f>
         <v>45925</v>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="15">
         <f t="shared" ref="G52" si="36">F52+1</f>
         <v>45926</v>
       </c>
-      <c r="H52" s="19">
+      <c r="H52" s="15">
         <f t="shared" ref="H52" si="37">G52+1</f>
         <v>45927</v>
       </c>
-      <c r="I52" s="19">
+      <c r="I52" s="15">
         <f t="shared" ref="I52" si="38">H52+1</f>
         <v>45928</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="18"/>
-      <c r="C53" s="20">
+      <c r="B53" s="25"/>
+      <c r="C53" s="16">
         <f>I44+1</f>
         <v>45922</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="16">
         <f>I44+2</f>
         <v>45923</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="16">
         <f>I44+3</f>
         <v>45924</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="16">
         <f>I44+4</f>
         <v>45925</v>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="16">
         <f>I44+5</f>
         <v>45926</v>
       </c>
-      <c r="H53" s="20">
+      <c r="H53" s="16">
         <f>I44+6</f>
         <v>45927</v>
       </c>
-      <c r="I53" s="20">
+      <c r="I53" s="16">
         <f>I44+7</f>
         <v>45928</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
     </row>
     <row r="55" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
     </row>
     <row r="56" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
     </row>
     <row r="57" spans="2:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="21">
         <f>C55-C54-C56</f>
         <v>0</v>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="21">
         <f>D55-D54-D56</f>
         <v>0</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="21">
         <f t="shared" ref="E57" si="39">E55-E54-E56</f>
         <v>0</v>
       </c>
-      <c r="F57" s="25">
+      <c r="F57" s="21">
         <f t="shared" ref="F57" si="40">F55-F54-F56</f>
         <v>0</v>
       </c>
-      <c r="G57" s="25">
+      <c r="G57" s="21">
         <f t="shared" ref="G57" si="41">G55-G54-G56</f>
         <v>0</v>
       </c>
-      <c r="H57" s="25">
+      <c r="H57" s="21">
         <f t="shared" ref="H57" si="42">H55-H54-H56</f>
         <v>0</v>
       </c>
-      <c r="I57" s="25">
+      <c r="I57" s="21">
         <f t="shared" ref="I57" si="43">I55-I54-I56</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:9" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
     </row>
     <row r="59" spans="2:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="26"/>
-      <c r="I59" s="26"/>
+      <c r="B59" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{09653C62-4CA3-4213-9539-CB60268A1635}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{25F40E88-8733-4112-BEE4-EDF2C692EE88}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -871,7 +871,7 @@
       <c r="C5" s="28"/>
       <c r="D5" s="11">
         <f>SUM(C12:I12)</f>
-        <v>0.27083333333333326</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E5" s="12">
         <f>SUM(C21:I21)</f>
@@ -895,7 +895,7 @@
       </c>
       <c r="J5" s="12">
         <f>SUM(D5:I5)</f>
-        <v>0.27083333333333326</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -978,7 +978,9 @@
       <c r="C9" s="18">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="18">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
@@ -992,7 +994,9 @@
       <c r="C10" s="18">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="18">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
@@ -1006,7 +1010,9 @@
       <c r="C11" s="19">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="19">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
@@ -1023,11 +1029,11 @@
         <v>0.27083333333333326</v>
       </c>
       <c r="D12" s="21">
-        <f t="shared" ref="D12:I12" si="1">D10-D9-D11</f>
-        <v>0</v>
+        <f>D10-D9-D11</f>
+        <v>0.33333333333333337</v>
       </c>
       <c r="E12" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D12:I12" si="1">E10-E9-E11</f>
         <v>0</v>
       </c>
       <c r="F12" s="21">

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{25F40E88-8733-4112-BEE4-EDF2C692EE88}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{170B98F0-F8DB-4613-8F04-A0320FFB3833}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31920" yWindow="3120" windowWidth="21600" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
   <si>
     <t>NOTES</t>
   </si>
@@ -95,6 +95,27 @@
   </si>
   <si>
     <t>Mise en place de scéance Jeudi 21 et Lundi 25</t>
+  </si>
+  <si>
+    <t>Fin schéma bloc 
+Recherche composants critiques 
+Création du schémas Altium
+Définission des questions
+Completions du schéma d'alimentations</t>
+  </si>
+  <si>
+    <t>Ajouter Resitance 19k1 sur buck down. 
+Ajout LDO low noise sur alim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting demain 16h30
+Passe la recherche sur AD7124 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion bloc entrée
+Recherche sur l'entrée et la schématique liées.
+Recherche sur l'etage ADC et choix du composants et la technologie
+Documentation </t>
   </si>
 </sst>
 </file>
@@ -106,7 +127,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="[$-40C]dddd"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -154,24 +175,37 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Corbel"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -270,7 +304,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -297,9 +331,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -312,43 +343,47 @@
     <xf numFmtId="20" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="18" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -439,7 +474,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>196011</xdr:colOff>
+      <xdr:colOff>196010</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>541923</xdr:rowOff>
     </xdr:to>
@@ -749,7 +784,7 @@
   <cols>
     <col min="1" max="1" width="3.375" customWidth="1"/>
     <col min="2" max="2" width="30.375" customWidth="1"/>
-    <col min="3" max="3" width="30.625" customWidth="1"/>
+    <col min="3" max="3" width="39.25" customWidth="1"/>
     <col min="4" max="4" width="37.875" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
     <col min="6" max="9" width="30.625" customWidth="1"/>
@@ -757,15 +792,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -793,19 +828,19 @@
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -828,74 +863,74 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" s="5" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:32" s="3" customFormat="1" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="23" t="s">
+      <c r="C4" s="28"/>
+      <c r="D4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="28">
+      <c r="B5" s="29">
         <v>45887</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="11">
+      <c r="C5" s="29"/>
+      <c r="D5" s="10">
         <f>SUM(C12:I12)</f>
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="E5" s="12">
+        <v>0.94791666666666652</v>
+      </c>
+      <c r="E5" s="11">
         <f>SUM(C21:I21)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <f>SUM(D30:I30)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <f>SUM(D39:I39)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f>SUM(D48:I48)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>SUM(D57:I57)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="11">
         <f>SUM(D5:I5)</f>
-        <v>0.60416666666666663</v>
+        <v>0.94791666666666652</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -908,7 +943,7 @@
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>1</v>
       </c>
       <c r="C7" s="15">
@@ -941,7 +976,7 @@
       </c>
     </row>
     <row r="8" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="25"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="16">
         <f>B5</f>
         <v>45887</v>
@@ -979,9 +1014,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="18">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E9" s="18"/>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E9" s="18">
+        <v>0.34375</v>
+      </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
@@ -995,9 +1032,11 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="D10" s="18">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E10" s="18"/>
+        <v>0.6875</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -1013,12 +1052,14 @@
       <c r="D11" s="19">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="19">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
-      <c r="J11" s="14"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
@@ -1030,11 +1071,11 @@
       </c>
       <c r="D12" s="21">
         <f>D10-D9-D11</f>
-        <v>0.33333333333333337</v>
+        <v>0.29166666666666663</v>
       </c>
       <c r="E12" s="21">
-        <f t="shared" ref="D12:I12" si="1">E10-E9-E11</f>
-        <v>0</v>
+        <f t="shared" ref="E12:I12" si="1">E10-E9-E11</f>
+        <v>0.38541666666666669</v>
       </c>
       <c r="F12" s="21">
         <f t="shared" si="1"/>
@@ -1053,45 +1094,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="212.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
+      <c r="D13" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-    </row>
-    <row r="15" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+      <c r="D14" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+    </row>
+    <row r="15" spans="1:32" ht="21" x14ac:dyDescent="0.35">
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <v>2</v>
       </c>
       <c r="C16" s="15">
@@ -1124,7 +1174,7 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="25"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="16">
         <f>I8+1</f>
         <v>45894</v>
@@ -1189,7 +1239,7 @@
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="20" t="s">
@@ -1228,29 +1278,38 @@
       <c r="B22" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-    </row>
-    <row r="24" spans="2:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+    </row>
+    <row r="24" spans="2:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+    </row>
     <row r="25" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <v>3</v>
       </c>
       <c r="C25" s="15">
@@ -1282,8 +1341,8 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="25"/>
+    <row r="26" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="26"/>
       <c r="C26" s="16">
         <f>I17+1</f>
         <v>45901</v>
@@ -1313,7 +1372,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B27" s="17" t="s">
         <v>2</v>
       </c>
@@ -1325,7 +1384,7 @@
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
     </row>
-    <row r="28" spans="2:10" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B28" s="17" t="s">
         <v>3</v>
       </c>
@@ -1337,7 +1396,7 @@
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
     </row>
-    <row r="29" spans="2:10" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B29" s="17" t="s">
         <v>8</v>
       </c>
@@ -1349,7 +1408,7 @@
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
     </row>
-    <row r="30" spans="2:10" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
         <v>4</v>
       </c>
@@ -1386,28 +1445,38 @@
       <c r="B31" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="2:10" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+    </row>
+    <row r="33" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <v>4</v>
       </c>
       <c r="C34" s="15">
@@ -1439,8 +1508,8 @@
         <v>45914</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="25"/>
+    <row r="35" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B35" s="26"/>
       <c r="C35" s="16">
         <f>I26+1</f>
         <v>45908</v>
@@ -1470,7 +1539,7 @@
         <v>45914</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B36" s="17" t="s">
         <v>2</v>
       </c>
@@ -1482,7 +1551,7 @@
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
     </row>
-    <row r="37" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B37" s="17" t="s">
         <v>3</v>
       </c>
@@ -1494,7 +1563,7 @@
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
     </row>
-    <row r="38" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B38" s="17" t="s">
         <v>8</v>
       </c>
@@ -1506,7 +1575,7 @@
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
     </row>
-    <row r="39" spans="2:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
         <v>4</v>
       </c>
@@ -1543,28 +1612,38 @@
       <c r="B40" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
     </row>
     <row r="41" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+    </row>
+    <row r="42" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
     </row>
     <row r="43" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="25">
+      <c r="B43" s="26">
         <v>5</v>
       </c>
       <c r="C43" s="15">
@@ -1596,8 +1675,8 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="25"/>
+    <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B44" s="26"/>
       <c r="C44" s="16">
         <f>I35+1</f>
         <v>45915</v>
@@ -1627,7 +1706,7 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B45" s="17" t="s">
         <v>2</v>
       </c>
@@ -1639,7 +1718,7 @@
       <c r="H45" s="18"/>
       <c r="I45" s="18"/>
     </row>
-    <row r="46" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="17" t="s">
         <v>3</v>
       </c>
@@ -1651,7 +1730,7 @@
       <c r="H46" s="18"/>
       <c r="I46" s="18"/>
     </row>
-    <row r="47" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="17" t="s">
         <v>8</v>
       </c>
@@ -1663,7 +1742,7 @@
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
     </row>
-    <row r="48" spans="2:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
         <v>4</v>
       </c>
@@ -1700,28 +1779,38 @@
       <c r="B49" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
     </row>
     <row r="50" spans="2:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
+    </row>
+    <row r="51" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
     </row>
     <row r="52" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="25">
+      <c r="B52" s="26">
         <v>6</v>
       </c>
       <c r="C52" s="15">
@@ -1753,8 +1842,8 @@
         <v>45928</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="25"/>
+    <row r="53" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B53" s="26"/>
       <c r="C53" s="16">
         <f>I44+1</f>
         <v>45922</v>
@@ -1784,7 +1873,7 @@
         <v>45928</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B54" s="17" t="s">
         <v>2</v>
       </c>
@@ -1796,7 +1885,7 @@
       <c r="H54" s="18"/>
       <c r="I54" s="18"/>
     </row>
-    <row r="55" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B55" s="17" t="s">
         <v>3</v>
       </c>
@@ -1808,7 +1897,7 @@
       <c r="H55" s="18"/>
       <c r="I55" s="18"/>
     </row>
-    <row r="56" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B56" s="17" t="s">
         <v>8</v>
       </c>
@@ -1820,7 +1909,7 @@
       <c r="H56" s="19"/>
       <c r="I56" s="19"/>
     </row>
-    <row r="57" spans="2:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
         <v>4</v>
       </c>
@@ -1857,25 +1946,25 @@
       <c r="B58" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
     </row>
     <row r="59" spans="2:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{170B98F0-F8DB-4613-8F04-A0320FFB3833}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{B588768A-73F5-4FDB-88AF-C5EA37E321C2}"/>
   <bookViews>
-    <workbookView xWindow="31920" yWindow="3120" windowWidth="21600" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -122,10 +122,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="[$-40C]dddd"/>
+    <numFmt numFmtId="168" formatCode="[hh]:mm"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -331,12 +332,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -391,6 +386,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -474,7 +475,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>196010</xdr:colOff>
+      <xdr:colOff>196011</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>541923</xdr:rowOff>
     </xdr:to>
@@ -787,20 +788,21 @@
     <col min="3" max="3" width="39.25" customWidth="1"/>
     <col min="4" max="4" width="37.875" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="9" width="30.625" customWidth="1"/>
+    <col min="6" max="6" width="44.5" customWidth="1"/>
+    <col min="7" max="9" width="30.625" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -828,19 +830,19 @@
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -863,74 +865,74 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" s="5" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:32" s="3" customFormat="1" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="29">
+      <c r="B5" s="27">
         <v>45887</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="10">
+      <c r="C5" s="27"/>
+      <c r="D5" s="29">
         <f>SUM(C12:I12)</f>
-        <v>0.94791666666666652</v>
-      </c>
-      <c r="E5" s="11">
+        <v>1.802083333333333</v>
+      </c>
+      <c r="E5" s="30">
         <f>SUM(C21:I21)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="30">
         <f>SUM(D30:I30)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="30">
         <f>SUM(D39:I39)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="30">
         <f>SUM(D48:I48)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="30">
         <f>SUM(D57:I57)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="30">
         <f>SUM(D5:I5)</f>
-        <v>0.94791666666666652</v>
+        <v>1.802083333333333</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -943,1028 +945,1040 @@
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="26">
+      <c r="B7" s="24">
         <v>1</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <f>B5</f>
         <v>45887</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <f>C7+1</f>
         <v>45888</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <f t="shared" ref="E7:I7" si="0">D7+1</f>
         <v>45889</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="13">
         <f t="shared" si="0"/>
         <v>45890</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="13">
         <f t="shared" si="0"/>
         <v>45891</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="13">
         <f t="shared" si="0"/>
         <v>45892</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <f t="shared" si="0"/>
         <v>45893</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="26"/>
-      <c r="C8" s="16">
+      <c r="B8" s="24"/>
+      <c r="C8" s="14">
         <f>B5</f>
         <v>45887</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="14">
         <f>B5+1</f>
         <v>45888</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <f>B5+2</f>
         <v>45889</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="14">
         <f>B5+3</f>
         <v>45890</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="14">
         <f>B5+4</f>
         <v>45891</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="14">
         <f>B5+5</f>
         <v>45892</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="14">
         <f>B5+6</f>
         <v>45893</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="16">
         <v>0.35416666666666669</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="16">
         <v>0.34375</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="F9" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="16">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="16">
         <v>0.6875</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="16">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="F10" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="17">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="17">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="17">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="13"/>
+      <c r="F11" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G11" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <f>C10-C9-C11</f>
         <v>0.27083333333333326</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="19">
         <f>D10-D9-D11</f>
         <v>0.29166666666666663</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="19">
         <f t="shared" ref="E12:I12" si="1">E10-E9-E11</f>
         <v>0.38541666666666669</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="21">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="G12" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="21">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H12" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="212.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" spans="1:32" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
     </row>
     <row r="15" spans="1:32" ht="21" x14ac:dyDescent="0.35">
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="26">
+      <c r="B16" s="24">
         <v>2</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <f>C17</f>
         <v>45894</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13">
         <f>C16+1</f>
         <v>45895</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="13">
         <f t="shared" ref="E16:I16" si="2">D16+1</f>
         <v>45896</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="13">
         <f t="shared" si="2"/>
         <v>45897</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="13">
         <f t="shared" si="2"/>
         <v>45898</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="13">
         <f t="shared" si="2"/>
         <v>45899</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="13">
         <f t="shared" si="2"/>
         <v>45900</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="26"/>
-      <c r="C17" s="16">
+      <c r="B17" s="24"/>
+      <c r="C17" s="14">
         <f>I8+1</f>
         <v>45894</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="14">
         <f>I8+2</f>
         <v>45895</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="14">
         <f>I8+3</f>
         <v>45896</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="14">
         <f>I8+4</f>
         <v>45897</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <f>I8+5</f>
         <v>45898</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="14">
         <f>I8+6</f>
         <v>45899</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="14">
         <f>I8+7</f>
         <v>45900</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="13"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <f>C19-C18-C20</f>
         <v>0</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="19">
         <f>D19-D18-D20</f>
         <v>0</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="19">
         <f t="shared" ref="E21:I21" si="3">E19-E18-E20</f>
         <v>0</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
     </row>
     <row r="23" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
+      <c r="B23" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
     </row>
     <row r="24" spans="2:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="26">
+      <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="13">
         <f>C26</f>
         <v>45901</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="13">
         <f>C25+1</f>
         <v>45902</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="13">
         <f t="shared" ref="E25" si="4">D25+1</f>
         <v>45903</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="13">
         <f t="shared" ref="F25" si="5">E25+1</f>
         <v>45904</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="13">
         <f t="shared" ref="G25" si="6">F25+1</f>
         <v>45905</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="13">
         <f t="shared" ref="H25" si="7">G25+1</f>
         <v>45906</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="13">
         <f t="shared" ref="I25" si="8">H25+1</f>
         <v>45907</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="16">
+      <c r="B26" s="24"/>
+      <c r="C26" s="14">
         <f>I17+1</f>
         <v>45901</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="14">
         <f>I17+2</f>
         <v>45902</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="14">
         <f>I17+3</f>
         <v>45903</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="14">
         <f>I17+4</f>
         <v>45904</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="14">
         <f>I17+5</f>
         <v>45905</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="14">
         <f>I17+6</f>
         <v>45906</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="14">
         <f>I17+7</f>
         <v>45907</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="19">
         <f>C28-C27-C29</f>
         <v>0</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="19">
         <f>D28-D27-D29</f>
         <v>0</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="19">
         <f t="shared" ref="E30" si="9">E28-E27-E29</f>
         <v>0</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="19">
         <f t="shared" ref="F30" si="10">F28-F27-F29</f>
         <v>0</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="19">
         <f t="shared" ref="G30" si="11">G28-G27-G29</f>
         <v>0</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="19">
         <f t="shared" ref="H30" si="12">H28-H27-H29</f>
         <v>0</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="19">
         <f t="shared" ref="I30" si="13">I28-I27-I29</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
     </row>
     <row r="32" spans="2:10" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
+      <c r="B32" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
     </row>
     <row r="33" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="26">
+      <c r="B34" s="24">
         <v>4</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="13">
         <f>C35</f>
         <v>45908</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="13">
         <f>C34+1</f>
         <v>45909</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="13">
         <f t="shared" ref="E34" si="14">D34+1</f>
         <v>45910</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="13">
         <f t="shared" ref="F34" si="15">E34+1</f>
         <v>45911</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="13">
         <f t="shared" ref="G34" si="16">F34+1</f>
         <v>45912</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="13">
         <f t="shared" ref="H34" si="17">G34+1</f>
         <v>45913</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="13">
         <f t="shared" ref="I34" si="18">H34+1</f>
         <v>45914</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B35" s="26"/>
-      <c r="C35" s="16">
+      <c r="B35" s="24"/>
+      <c r="C35" s="14">
         <f>I26+1</f>
         <v>45908</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="14">
         <f>I26+2</f>
         <v>45909</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="14">
         <f>I26+3</f>
         <v>45910</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="14">
         <f>I26+4</f>
         <v>45911</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="14">
         <f>I26+5</f>
         <v>45912</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="14">
         <f>I26+6</f>
         <v>45913</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="14">
         <f>I26+7</f>
         <v>45914</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
     </row>
     <row r="37" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
     </row>
     <row r="38" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="19">
         <f>C37-C36-C38</f>
         <v>0</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="19">
         <f>D37-D36-D38</f>
         <v>0</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="19">
         <f t="shared" ref="E39" si="19">E37-E36-E38</f>
         <v>0</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="19">
         <f t="shared" ref="F39" si="20">F37-F36-F38</f>
         <v>0</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="19">
         <f t="shared" ref="G39" si="21">G37-G36-G38</f>
         <v>0</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="19">
         <f t="shared" ref="H39" si="22">H37-H36-H38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="19">
         <f t="shared" ref="I39" si="23">I37-I36-I38</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
     </row>
     <row r="41" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
+      <c r="B41" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
     </row>
     <row r="42" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
     </row>
     <row r="43" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="26">
+      <c r="B43" s="24">
         <v>5</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="13">
         <f>C44</f>
         <v>45915</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="13">
         <f>C43+1</f>
         <v>45916</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="13">
         <f t="shared" ref="E43" si="24">D43+1</f>
         <v>45917</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="13">
         <f t="shared" ref="F43" si="25">E43+1</f>
         <v>45918</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="13">
         <f t="shared" ref="G43" si="26">F43+1</f>
         <v>45919</v>
       </c>
-      <c r="H43" s="15">
+      <c r="H43" s="13">
         <f t="shared" ref="H43" si="27">G43+1</f>
         <v>45920</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="13">
         <f t="shared" ref="I43" si="28">H43+1</f>
         <v>45921</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="26"/>
-      <c r="C44" s="16">
+      <c r="B44" s="24"/>
+      <c r="C44" s="14">
         <f>I35+1</f>
         <v>45915</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="14">
         <f>I35+2</f>
         <v>45916</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="14">
         <f>I35+3</f>
         <v>45917</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="14">
         <f>I35+4</f>
         <v>45918</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="14">
         <f>I35+5</f>
         <v>45919</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="14">
         <f>I35+6</f>
         <v>45920</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="14">
         <f>I35+7</f>
         <v>45921</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
     </row>
     <row r="47" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
     </row>
     <row r="48" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="19">
         <f>C46-C45-C47</f>
         <v>0</v>
       </c>
-      <c r="D48" s="21">
+      <c r="D48" s="19">
         <f>D46-D45-D47</f>
         <v>0</v>
       </c>
-      <c r="E48" s="21">
+      <c r="E48" s="19">
         <f t="shared" ref="E48" si="29">E46-E45-E47</f>
         <v>0</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="19">
         <f t="shared" ref="F48" si="30">F46-F45-F47</f>
         <v>0</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="19">
         <f t="shared" ref="G48" si="31">G46-G45-G47</f>
         <v>0</v>
       </c>
-      <c r="H48" s="21">
+      <c r="H48" s="19">
         <f t="shared" ref="H48" si="32">H46-H45-H47</f>
         <v>0</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="19">
         <f t="shared" ref="I48" si="33">I46-I45-I47</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
     </row>
     <row r="50" spans="2:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
+      <c r="B50" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
     </row>
     <row r="51" spans="2:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
     </row>
     <row r="52" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="26">
+      <c r="B52" s="24">
         <v>6</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="13">
         <f>C53</f>
         <v>45922</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="13">
         <f>C52+1</f>
         <v>45923</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="13">
         <f t="shared" ref="E52" si="34">D52+1</f>
         <v>45924</v>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="13">
         <f t="shared" ref="F52" si="35">E52+1</f>
         <v>45925</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="13">
         <f t="shared" ref="G52" si="36">F52+1</f>
         <v>45926</v>
       </c>
-      <c r="H52" s="15">
+      <c r="H52" s="13">
         <f t="shared" ref="H52" si="37">G52+1</f>
         <v>45927</v>
       </c>
-      <c r="I52" s="15">
+      <c r="I52" s="13">
         <f t="shared" ref="I52" si="38">H52+1</f>
         <v>45928</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="26"/>
-      <c r="C53" s="16">
+      <c r="B53" s="24"/>
+      <c r="C53" s="14">
         <f>I44+1</f>
         <v>45922</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="14">
         <f>I44+2</f>
         <v>45923</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="14">
         <f>I44+3</f>
         <v>45924</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="14">
         <f>I44+4</f>
         <v>45925</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="14">
         <f>I44+5</f>
         <v>45926</v>
       </c>
-      <c r="H53" s="16">
+      <c r="H53" s="14">
         <f>I44+6</f>
         <v>45927</v>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="14">
         <f>I44+7</f>
         <v>45928</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
     </row>
     <row r="55" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
     </row>
     <row r="56" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
     </row>
     <row r="57" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C57" s="21">
+      <c r="C57" s="19">
         <f>C55-C54-C56</f>
         <v>0</v>
       </c>
-      <c r="D57" s="21">
+      <c r="D57" s="19">
         <f>D55-D54-D56</f>
         <v>0</v>
       </c>
-      <c r="E57" s="21">
+      <c r="E57" s="19">
         <f t="shared" ref="E57" si="39">E55-E54-E56</f>
         <v>0</v>
       </c>
-      <c r="F57" s="21">
+      <c r="F57" s="19">
         <f t="shared" ref="F57" si="40">F55-F54-F56</f>
         <v>0</v>
       </c>
-      <c r="G57" s="21">
+      <c r="G57" s="19">
         <f t="shared" ref="G57" si="41">G55-G54-G56</f>
         <v>0</v>
       </c>
-      <c r="H57" s="21">
+      <c r="H57" s="19">
         <f t="shared" ref="H57" si="42">H55-H54-H56</f>
         <v>0</v>
       </c>
-      <c r="I57" s="21">
+      <c r="I57" s="19">
         <f t="shared" ref="I57" si="43">I55-I54-I56</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:9" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" spans="2:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
+      <c r="B59" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{B588768A-73F5-4FDB-88AF-C5EA37E321C2}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{C22D6F8A-7258-4AC7-8174-6C50F0ACAEE4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
   <si>
     <t>NOTES</t>
   </si>
@@ -116,6 +116,45 @@
 Recherche sur l'entrée et la schématique liées.
 Recherche sur l'etage ADC et choix du composants et la technologie
 Documentation </t>
+  </si>
+  <si>
+    <t>Fin recherche composant ADC
+Dimensionnement ADC
+Dimensionnement et ajout des I/O du CM5
+Ajout de l'USB
+Meeting de design avec retour sur les différents éléments</t>
+  </si>
+  <si>
+    <t>ADC prix ok
+Ajout USB pour programmation 
+Ethernet en 2 paires 
+Passage du relais sur carte fille</t>
+  </si>
+  <si>
+    <t>Design carte fille
+Ajout des relais
+Recherche solution pour le mux
+Ajout des réseau de résistance
+Début rapport
+Création PV 22.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solution MUX complex, influence de la résitance interne sur le réseau. </t>
+  </si>
+  <si>
+    <t>Solution pour le mux proposée
+Reflection etage de sortie 24V
+Liens des schémas
+Rapport 
+PV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mux cher 15.- ? Meillieur solution ?
+Sortie 24V doivent lire une tension ou injecter un courant ? Influence sur le systèmes actif ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revue de schéma
+</t>
   </si>
 </sst>
 </file>
@@ -126,7 +165,7 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="[$-40C]dddd"/>
-    <numFmt numFmtId="168" formatCode="[hh]:mm"/>
+    <numFmt numFmtId="167" formatCode="[hh]:mm"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -372,6 +411,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -386,12 +431,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -474,8 +513,8 @@
       <xdr:rowOff>132291</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>196011</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2533965</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>541923</xdr:rowOff>
     </xdr:to>
@@ -789,20 +828,22 @@
     <col min="4" max="4" width="37.875" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
     <col min="6" max="6" width="44.5" customWidth="1"/>
-    <col min="7" max="9" width="30.625" customWidth="1"/>
+    <col min="7" max="7" width="47" customWidth="1"/>
+    <col min="8" max="8" width="46.875" customWidth="1"/>
+    <col min="9" max="9" width="47.875" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -865,20 +906,20 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" s="5" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:32" s="3" customFormat="1" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="26"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="12" t="s">
         <v>15</v>
       </c>
@@ -902,37 +943,37 @@
       </c>
     </row>
     <row r="5" spans="1:32" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <v>45887</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="29">
+      <c r="C5" s="29"/>
+      <c r="D5" s="24">
         <f>SUM(C12:I12)</f>
-        <v>1.802083333333333</v>
-      </c>
-      <c r="E5" s="30">
+        <v>2.177083333333333</v>
+      </c>
+      <c r="E5" s="25">
         <f>SUM(C21:I21)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="30">
+        <v>1.1041666666666667</v>
+      </c>
+      <c r="F5" s="25">
         <f>SUM(D30:I30)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="25">
         <f>SUM(D39:I39)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="25">
         <f>SUM(D48:I48)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="25">
         <f>SUM(D57:I57)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>1.802083333333333</v>
+        <v>3.28125</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -945,7 +986,7 @@
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <v>1</v>
       </c>
       <c r="C7" s="13">
@@ -978,7 +1019,7 @@
       </c>
     </row>
     <row r="8" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="24"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="14">
         <f>B5</f>
         <v>45887</v>
@@ -1028,7 +1069,9 @@
         <v>0.34375</v>
       </c>
       <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="I9" s="16">
+        <v>0.45833333333333331</v>
+      </c>
     </row>
     <row r="10" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
@@ -1050,7 +1093,9 @@
         <v>0.8125</v>
       </c>
       <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="I10" s="16">
+        <v>0.91666666666666663</v>
+      </c>
     </row>
     <row r="11" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="s">
@@ -1072,7 +1117,9 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
+      <c r="I11" s="17">
+        <v>8.3333333333333329E-2</v>
+      </c>
       <c r="J11" s="11"/>
     </row>
     <row r="12" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1105,7 +1152,7 @@
       </c>
       <c r="I12" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="212.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1121,10 +1168,16 @@
       <c r="E13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="F13" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>24</v>
+      </c>
       <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
+      <c r="I13" s="21" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:32" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
@@ -1139,10 +1192,16 @@
       <c r="E14" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
+      <c r="F14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
+      <c r="I14" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:32" ht="21" x14ac:dyDescent="0.35">
       <c r="B15" s="22"/>
@@ -1155,7 +1214,7 @@
       <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:32" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="24">
+      <c r="B16" s="26">
         <v>2</v>
       </c>
       <c r="C16" s="13">
@@ -1188,7 +1247,7 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="24"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="14">
         <f>I8+1</f>
         <v>45894</v>
@@ -1222,9 +1281,15 @@
       <c r="B18" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="C18" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0.34375</v>
+      </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
@@ -1234,9 +1299,15 @@
       <c r="B19" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
+      <c r="C19" s="16">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D19" s="16">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E19" s="16">
+        <v>0.71875</v>
+      </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
@@ -1246,9 +1317,15 @@
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D20" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E20" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
@@ -1261,15 +1338,15 @@
       </c>
       <c r="C21" s="19">
         <f>C19-C18-C20</f>
-        <v>0</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="D21" s="19">
         <f>D19-D18-D20</f>
-        <v>0</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="E21" s="19">
         <f t="shared" ref="E21:I21" si="3">E19-E18-E20</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F21" s="19">
         <f t="shared" si="3"/>
@@ -1292,7 +1369,9 @@
       <c r="B22" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="21"/>
+      <c r="C22" s="21" t="s">
+        <v>28</v>
+      </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
@@ -1323,7 +1402,7 @@
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="24">
+      <c r="B25" s="26">
         <v>3</v>
       </c>
       <c r="C25" s="13">
@@ -1356,7 +1435,7 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="24"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="14">
         <f>I17+1</f>
         <v>45901</v>
@@ -1490,7 +1569,7 @@
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="24">
+      <c r="B34" s="26">
         <v>4</v>
       </c>
       <c r="C34" s="13">
@@ -1523,7 +1602,7 @@
       </c>
     </row>
     <row r="35" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B35" s="24"/>
+      <c r="B35" s="26"/>
       <c r="C35" s="14">
         <f>I26+1</f>
         <v>45908</v>
@@ -1657,7 +1736,7 @@
       <c r="I42" s="22"/>
     </row>
     <row r="43" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="24">
+      <c r="B43" s="26">
         <v>5</v>
       </c>
       <c r="C43" s="13">
@@ -1690,7 +1769,7 @@
       </c>
     </row>
     <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="24"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="14">
         <f>I35+1</f>
         <v>45915</v>
@@ -1824,7 +1903,7 @@
       <c r="I51" s="22"/>
     </row>
     <row r="52" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="24">
+      <c r="B52" s="26">
         <v>6</v>
       </c>
       <c r="C52" s="13">
@@ -1857,7 +1936,7 @@
       </c>
     </row>
     <row r="53" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="24"/>
+      <c r="B53" s="26"/>
       <c r="C53" s="14">
         <f>I44+1</f>
         <v>45922</v>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{C22D6F8A-7258-4AC7-8174-6C50F0ACAEE4}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15C0AA5-BA76-4C2F-8BC2-3B45E66D0AD6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>NOTES</t>
   </si>
@@ -153,8 +153,31 @@
 Sortie 24V doivent lire une tension ou injecter un courant ? Influence sur le systèmes actif ? </t>
   </si>
   <si>
-    <t xml:space="preserve">Revue de schéma
-</t>
+    <t>Revue de schéma
+Correction schéma</t>
+  </si>
+  <si>
+    <t>Confirmer nouvelle approche avec Rref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation tecchnique Rref en changeant l'excel de clacul 
+Vérification et correction des erreurs abordée lors de la revue de schéma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création des boms
+Récupération, vérifications et ajout des footprints
+Documentations 
+Calcul des consomations et vérifications des dimensionnements </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation rapport toujours sur le design, a reprendre </t>
+  </si>
+  <si>
+    <t>Boms et vérifications 
+Reflections mécanique 
+Crélation des PCB 
+Avançée sur le rapport 
+Réeunion de suivit</t>
   </si>
 </sst>
 </file>
@@ -953,7 +976,7 @@
       </c>
       <c r="E5" s="25">
         <f>SUM(C21:I21)</f>
-        <v>1.1041666666666667</v>
+        <v>1.8125</v>
       </c>
       <c r="F5" s="25">
         <f>SUM(D30:I30)</f>
@@ -973,7 +996,7 @@
       </c>
       <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>3.28125</v>
+        <v>3.989583333333333</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1290,8 +1313,12 @@
       <c r="E18" s="16">
         <v>0.34375</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="F18" s="16">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="H18" s="16"/>
       <c r="I18" s="16"/>
     </row>
@@ -1308,8 +1335,12 @@
       <c r="E19" s="16">
         <v>0.71875</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="F19" s="16">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
     </row>
@@ -1326,8 +1357,12 @@
       <c r="E20" s="17">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="F20" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G20" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="11"/>
@@ -1350,11 +1385,11 @@
       </c>
       <c r="F21" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="G21" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="H21" s="19">
         <f t="shared" si="3"/>
@@ -1365,16 +1400,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" ht="159" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
+      <c r="D22" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>33</v>
+      </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
       <c r="I22" s="21"/>
@@ -1383,9 +1424,13 @@
       <c r="B23" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="21"/>
+      <c r="C23" s="21" t="s">
+        <v>29</v>
+      </c>
       <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="E23" s="21" t="s">
+        <v>32</v>
+      </c>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15C0AA5-BA76-4C2F-8BC2-3B45E66D0AD6}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C0435DE-F79B-4EB9-8D72-D96CBC6DC549}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t>NOTES</t>
   </si>
@@ -178,6 +178,31 @@
 Crélation des PCB 
 Avançée sur le rapport 
 Réeunion de suivit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB Fille
+Création PCB carte mère
+Reflection mecanique
+Placement </t>
+  </si>
+  <si>
+    <t>Routage carte fille
+Correction Design Rule Check</t>
+  </si>
+  <si>
+    <t>Rapport fin partie design
+PV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation PCB
+Envois pour revue 
+Flasher CM5
+Reflection architechture de développement </t>
+  </si>
+  <si>
+    <t>Réunion review layout 
+Test outils de développement remote
+Reflection C/Python</t>
   </si>
 </sst>
 </file>
@@ -976,11 +1001,11 @@
       </c>
       <c r="E5" s="25">
         <f>SUM(C21:I21)</f>
-        <v>1.8125</v>
+        <v>2.0625</v>
       </c>
       <c r="F5" s="25">
         <f>SUM(D30:I30)</f>
-        <v>0</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="G5" s="25">
         <f>SUM(D39:I39)</f>
@@ -996,7 +1021,7 @@
       </c>
       <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>3.989583333333333</v>
+        <v>5.03125</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1320,7 +1345,9 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
+      <c r="I18" s="16">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="19" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
@@ -1342,7 +1369,9 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+      <c r="I19" s="16">
+        <v>0.95833333333333337</v>
+      </c>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
@@ -1364,7 +1393,9 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="I20" s="17">
+        <v>8.3333333333333329E-2</v>
+      </c>
       <c r="J20" s="11"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1397,7 +1428,7 @@
       </c>
       <c r="I21" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25000000000000006</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="159" customHeight="1" x14ac:dyDescent="0.25">
@@ -1416,9 +1447,13 @@
       <c r="F22" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="21"/>
+      <c r="G22" s="21" t="s">
+        <v>34</v>
+      </c>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
+      <c r="I22" s="21" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="23" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
@@ -1514,9 +1549,15 @@
       <c r="B27" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="C27" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="D27" s="16">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="E27" s="16">
+        <v>0.34375</v>
+      </c>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
@@ -1526,9 +1567,15 @@
       <c r="B28" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="C28" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="D28" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="E28" s="16">
+        <v>0.8125</v>
+      </c>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
@@ -1538,9 +1585,15 @@
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="C29" s="17">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D29" s="17">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E29" s="17">
+        <v>6.25E-2</v>
+      </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
@@ -1552,15 +1605,15 @@
       </c>
       <c r="C30" s="19">
         <f>C28-C27-C29</f>
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="D30" s="19">
         <f>D28-D27-D29</f>
-        <v>0</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="E30" s="19">
         <f t="shared" ref="E30" si="9">E28-E27-E29</f>
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="F30" s="19">
         <f t="shared" ref="F30" si="10">F28-F27-F29</f>
@@ -1579,19 +1632,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="C31" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>38</v>
+      </c>
       <c r="F31" s="21"/>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
       <c r="I31" s="21"/>
     </row>
-    <row r="32" spans="2:10" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>0</v>
       </c>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C0435DE-F79B-4EB9-8D72-D96CBC6DC549}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{534355FB-36BE-4662-AAC0-899C9F78AE4C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
   <si>
     <t>NOTES</t>
   </si>
@@ -202,7 +202,12 @@
   <si>
     <t>Réunion review layout 
 Test outils de développement remote
-Reflection C/Python</t>
+Reflection C/Python
+Correction Layout
+Pannel</t>
+  </si>
+  <si>
+    <t>Modification pannel pour commander</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1010,7 @@
       </c>
       <c r="F5" s="25">
         <f>SUM(D30:I30)</f>
-        <v>0.79166666666666674</v>
+        <v>1.28125</v>
       </c>
       <c r="G5" s="25">
         <f>SUM(D39:I39)</f>
@@ -1021,7 +1026,7 @@
       </c>
       <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>5.03125</v>
+        <v>5.520833333333333</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1558,7 +1563,9 @@
       <c r="E27" s="16">
         <v>0.34375</v>
       </c>
-      <c r="F27" s="16"/>
+      <c r="F27" s="16">
+        <v>0.34375</v>
+      </c>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
@@ -1574,9 +1581,11 @@
         <v>0.8125</v>
       </c>
       <c r="E28" s="16">
-        <v>0.8125</v>
-      </c>
-      <c r="F28" s="16"/>
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0.85416666666666663</v>
+      </c>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
       <c r="I28" s="16"/>
@@ -1594,7 +1603,9 @@
       <c r="E29" s="17">
         <v>6.25E-2</v>
       </c>
-      <c r="F29" s="17"/>
+      <c r="F29" s="17">
+        <v>6.25E-2</v>
+      </c>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
@@ -1613,11 +1624,11 @@
       </c>
       <c r="E30" s="19">
         <f t="shared" ref="E30" si="9">E28-E27-E29</f>
-        <v>0.40625</v>
+        <v>0.44791666666666663</v>
       </c>
       <c r="F30" s="19">
         <f t="shared" ref="F30" si="10">F28-F27-F29</f>
-        <v>0</v>
+        <v>0.44791666666666663</v>
       </c>
       <c r="G30" s="19">
         <f t="shared" ref="G30" si="11">G28-G27-G29</f>
@@ -1645,7 +1656,9 @@
       <c r="E31" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="21"/>
+      <c r="F31" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
       <c r="I31" s="21"/>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{534355FB-36BE-4662-AAC0-899C9F78AE4C}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB2FC66-CC83-43FA-AF9E-DECA1F9F2BF3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -207,7 +207,10 @@
 Pannel</t>
   </si>
   <si>
-    <t>Modification pannel pour commander</t>
+    <t xml:space="preserve">Modification pannel pour commander
+Mise en place de pycharm 
+Test script python simple 
+Correction comamdne composants </t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1013,7 @@
       </c>
       <c r="F5" s="25">
         <f>SUM(D30:I30)</f>
-        <v>1.28125</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="25">
         <f>SUM(D39:I39)</f>
@@ -1026,7 +1029,7 @@
       </c>
       <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>5.520833333333333</v>
+        <v>5.739583333333333</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1566,7 +1569,9 @@
       <c r="F27" s="16">
         <v>0.34375</v>
       </c>
-      <c r="G27" s="16"/>
+      <c r="G27" s="16">
+        <v>0.36458333333333331</v>
+      </c>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
     </row>
@@ -1584,9 +1589,11 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="F28" s="16">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="G28" s="16"/>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="H28" s="16"/>
       <c r="I28" s="16"/>
     </row>
@@ -1604,9 +1611,11 @@
         <v>6.25E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>6.25E-2</v>
-      </c>
-      <c r="G29" s="17"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G29" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
     </row>
@@ -1628,11 +1637,11 @@
       </c>
       <c r="F30" s="19">
         <f t="shared" ref="F30" si="10">F28-F27-F29</f>
-        <v>0.44791666666666663</v>
+        <v>0.34374999999999994</v>
       </c>
       <c r="G30" s="19">
         <f t="shared" ref="G30" si="11">G28-G27-G29</f>
-        <v>0</v>
+        <v>0.32291666666666663</v>
       </c>
       <c r="H30" s="19">
         <f t="shared" ref="H30" si="12">H28-H27-H29</f>
@@ -1643,7 +1652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" ht="222.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>5</v>
       </c>
@@ -1663,7 +1672,7 @@
       <c r="H31" s="21"/>
       <c r="I31" s="21"/>
     </row>
-    <row r="32" spans="2:10" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>0</v>
       </c>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB2FC66-CC83-43FA-AF9E-DECA1F9F2BF3}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{13853B49-7B13-4BE1-B376-5FA83F0429DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
   <si>
     <t>NOTES</t>
   </si>
@@ -211,6 +211,23 @@
 Mise en place de pycharm 
 Test script python simple 
 Correction comamdne composants </t>
+  </si>
+  <si>
+    <t>Déverloppemment de logique software. 
+Realease des PCB sur altiums 
+Corrections de la documentations avec les dernière moddifications effectuée
+Présentation du projets à l'expert M. Moeschler</t>
+  </si>
+  <si>
+    <t>Documentation avançée sur le rapport</t>
+  </si>
+  <si>
+    <t>Partie layout et mecanique rapport 
+Programmation script python 
+Reception composants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomamnder composants inductance car erreur de commandes </t>
   </si>
 </sst>
 </file>
@@ -430,7 +447,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1012,24 +1029,24 @@
         <v>2.0625</v>
       </c>
       <c r="F5" s="25">
-        <f>SUM(D30:I30)</f>
-        <v>1.5</v>
+        <f>SUM(C30:I30)</f>
+        <v>2.09375</v>
       </c>
       <c r="G5" s="25">
-        <f>SUM(D39:I39)</f>
-        <v>0</v>
+        <f>SUM(C39:I39)</f>
+        <v>0.34374999999999994</v>
       </c>
       <c r="H5" s="25">
-        <f>SUM(D48:I48)</f>
+        <f>SUM(C48:I48)</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
-        <f>SUM(D57:I57)</f>
+        <f>SUM(C57:I57)</f>
         <v>0</v>
       </c>
       <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>5.739583333333333</v>
+        <v>6.677083333333333</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1573,7 +1590,9 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
+      <c r="I27" s="16">
+        <v>0.60416666666666663</v>
+      </c>
     </row>
     <row r="28" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
@@ -1595,7 +1614,9 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
+      <c r="I28" s="16">
+        <v>0.83333333333333337</v>
+      </c>
     </row>
     <row r="29" spans="2:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
@@ -1617,7 +1638,9 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
+      <c r="I29" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
     </row>
     <row r="30" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="s">
@@ -1649,7 +1672,7 @@
       </c>
       <c r="I30" s="19">
         <f t="shared" ref="I30" si="13">I28-I27-I29</f>
-        <v>0</v>
+        <v>0.18750000000000008</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="222.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1668,9 +1691,13 @@
       <c r="F31" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="21"/>
+      <c r="G31" s="21" t="s">
+        <v>40</v>
+      </c>
       <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
+      <c r="I31" s="21" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="32" spans="2:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
@@ -1762,7 +1789,9 @@
       <c r="B36" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="16"/>
+      <c r="C36" s="16">
+        <v>0.34375</v>
+      </c>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
@@ -1774,7 +1803,9 @@
       <c r="B37" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="16"/>
+      <c r="C37" s="16">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
@@ -1786,7 +1817,9 @@
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="17"/>
+      <c r="C38" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
@@ -1800,7 +1833,7 @@
       </c>
       <c r="C39" s="19">
         <f>C37-C36-C38</f>
-        <v>0</v>
+        <v>0.34374999999999994</v>
       </c>
       <c r="D39" s="19">
         <f>D37-D36-D38</f>
@@ -1827,11 +1860,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="21"/>
+      <c r="C40" s="21" t="s">
+        <v>42</v>
+      </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
@@ -1843,7 +1878,9 @@
       <c r="B41" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="21"/>
+      <c r="C41" s="21" t="s">
+        <v>43</v>
+      </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{13853B49-7B13-4BE1-B376-5FA83F0429DD}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{45023EDD-0DDC-461A-BF6A-41CAE4995C50}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>NOTES</t>
   </si>
@@ -88,20 +88,7 @@
     <t>SEMAINE 1</t>
   </si>
   <si>
-    <t>Reception Cahier des charges et consignes. 
-Meeting avec M.Graf et M. Bovet.  Présenrtation du cahier des charges, questions et réponses. 
-Création des documentations.
-Pré-études avec schéma bloc</t>
-  </si>
-  <si>
     <t>Mise en place de scéance Jeudi 21 et Lundi 25</t>
-  </si>
-  <si>
-    <t>Fin schéma bloc 
-Recherche composants critiques 
-Création du schémas Altium
-Définission des questions
-Completions du schéma d'alimentations</t>
   </si>
   <si>
     <t>Ajouter Resitance 19k1 sur buck down. 
@@ -110,19 +97,6 @@
   <si>
     <t xml:space="preserve">Meeting demain 16h30
 Passe la recherche sur AD7124 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completion bloc entrée
-Recherche sur l'entrée et la schématique liées.
-Recherche sur l'etage ADC et choix du composants et la technologie
-Documentation </t>
-  </si>
-  <si>
-    <t>Fin recherche composant ADC
-Dimensionnement ADC
-Dimensionnement et ajout des I/O du CM5
-Ajout de l'USB
-Meeting de design avec retour sur les différents éléments</t>
   </si>
   <si>
     <t>ADC prix ok
@@ -131,103 +105,185 @@
 Passage du relais sur carte fille</t>
   </si>
   <si>
-    <t>Design carte fille
-Ajout des relais
-Recherche solution pour le mux
-Ajout des réseau de résistance
-Début rapport
-Création PV 22.08.2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution MUX complex, influence de la résitance interne sur le réseau. </t>
-  </si>
-  <si>
-    <t>Solution pour le mux proposée
-Reflection etage de sortie 24V
-Liens des schémas
-Rapport 
-PV</t>
   </si>
   <si>
     <t xml:space="preserve">Mux cher 15.- ? Meillieur solution ?
 Sortie 24V doivent lire une tension ou injecter un courant ? Influence sur le systèmes actif ? </t>
   </si>
   <si>
-    <t>Revue de schéma
-Correction schéma</t>
-  </si>
-  <si>
     <t>Confirmer nouvelle approche avec Rref</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmation tecchnique Rref en changeant l'excel de clacul 
-Vérification et correction des erreurs abordée lors de la revue de schéma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création des boms
-Récupération, vérifications et ajout des footprints
-Documentations 
-Calcul des consomations et vérifications des dimensionnements </t>
-  </si>
-  <si>
     <t xml:space="preserve">Documentation rapport toujours sur le design, a reprendre </t>
   </si>
   <si>
-    <t>Boms et vérifications 
-Reflections mécanique 
-Crélation des PCB 
-Avançée sur le rapport 
-Réeunion de suivit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCB Fille
-Création PCB carte mère
-Reflection mecanique
-Placement </t>
-  </si>
-  <si>
-    <t>Routage carte fille
-Correction Design Rule Check</t>
-  </si>
-  <si>
-    <t>Rapport fin partie design
+    <t xml:space="preserve">Recommander composants inductance car erreur de commandes </t>
+  </si>
+  <si>
+    <t>Equipement un peu limite enpêchant une bonne qualité de productions</t>
+  </si>
+  <si>
+    <t>L'USB C n'a pas tenu le dépannage. Monté USB-C + coonetique CM5 sur seconde carte pour prover fonctionnement</t>
+  </si>
+  <si>
+    <t>•Reception Cahier des charges et consignes. 
+Meeting avec M.Graf et M. Bovet.  
+•Présenrtation du cahier des charges, questions et réponses. 
+•Création des documentations.
+Pré-études avec schéma bloc</t>
+  </si>
+  <si>
+    <t>•Fin schéma bloc 
+•Recherche composants critiques 
+•Création du schémas Altium
+•Définission des questions
+•Completions du schéma d'alimentations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Completion bloc entrée
+•Recherche sur l'entrée et la schématique liées.
+•Recherche sur l'etage ADC et choix du composants et la technologie
+•Documentation </t>
+  </si>
+  <si>
+    <t>•Fin recherche composant ADC
+•Dimensionnement ADC
+•Dimensionnement et ajout des I/O du CM5
+•Ajout de l'USB
+•Meeting de design avec retour sur les différents éléments</t>
+  </si>
+  <si>
+    <t>•Design carte fille
+•Ajout des relais
+•Recherche solution pour le mux
+•Ajout des réseau de résistance
+•Début rapport
+•Création PV 22.08.2025</t>
+  </si>
+  <si>
+    <t>•Solution pour le mux proposée
+•Reflection etage de sortie 24V
+•Liens des schémas
+•Rapport 
+•PV</t>
+  </si>
+  <si>
+    <t>•Revue de schéma
+•Correction schéma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Confirmation tecchnique •Rref en changeant l'excel de clacul 
+•Vérification et correction des erreurs abordée lors de la revue de schéma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Création des boms
+•Récupération, vérifications et ajout des footprints
+•Documentations 
+•Calcul des consomations et vérifications des dimensionnements </t>
+  </si>
+  <si>
+    <t>•Boms et vérifications 
+•Reflections mécanique 
+•Crélation des PCB 
+•Avançée sur le rapport 
+•Réeunion de suivit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•PCB Fille
+•Création PCB carte mère
+•Reflection mecanique
+•Placement </t>
+  </si>
+  <si>
+    <t>• Rapport fin partie design
 PV</t>
   </si>
   <si>
-    <t xml:space="preserve">Finalisation PCB
-Envois pour revue 
-Flasher CM5
-Reflection architechture de développement </t>
-  </si>
-  <si>
-    <t>Réunion review layout 
-Test outils de développement remote
-Reflection C/Python
-Correction Layout
+    <t>•Routage carte fille
+•Correction Design Rule Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Finalisation PCB
+•Envois pour revue 
+•Flasher CM5
+•Reflection architechture de développement </t>
+  </si>
+  <si>
+    <t>•Réunion review layout 
+•Test outils de développement remote
+•Reflection C/Python
+•Correction Layout
 Pannel</t>
   </si>
   <si>
-    <t xml:space="preserve">Modification pannel pour commander
-Mise en place de pycharm 
-Test script python simple 
-Correction comamdne composants </t>
-  </si>
-  <si>
-    <t>Déverloppemment de logique software. 
-Realease des PCB sur altiums 
-Corrections de la documentations avec les dernière moddifications effectuée
-Présentation du projets à l'expert M. Moeschler</t>
-  </si>
-  <si>
-    <t>Documentation avançée sur le rapport</t>
-  </si>
-  <si>
-    <t>Partie layout et mecanique rapport 
-Programmation script python 
-Reception composants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recomamnder composants inductance car erreur de commandes </t>
+    <t xml:space="preserve">•Modification pannel pour commander
+•Mise en place de pycharm 
+•Test script python simple 
+•Correction comamdne composants </t>
+  </si>
+  <si>
+    <t>•Déverloppemment de logique software. 
+•Realease des PCB sur altiums 
+•Corrections de la documentations avec les dernière moddifications effectuée
+•Présentation du projets à l'expert M. Moeschler</t>
+  </si>
+  <si>
+    <t>•Documentation avançée sur le rapport</t>
+  </si>
+  <si>
+    <t>•Partie layout et mecanique rapport 
+•Programmation script python 
+•Reception composants</t>
+  </si>
+  <si>
+    <t>•Programation test SPI avec LM70. 
+•Développment logique de programmation diagram UML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Développment logique de programmation diagram UML 
+•Récéptions PCB 
+•Réunion de suivis 
+•Brasage composant critique au stencil + four </t>
+  </si>
+  <si>
+    <t>•Problème USB brassé - court circuit. 
+•Montage d'une carte fille et une carte mère. 
+•Ajout commande nouveua connecteur berg CM5 et résistance 19k1 non commandé</t>
+  </si>
+  <si>
+    <t>•Mise en service, test du montage , test CM5 , test alimentations partie 3V3
+•Dévelopment Code test SPI sur le MUX et ADC</t>
+  </si>
+  <si>
+    <t>Le MUX et l'ADC communique. 
+Le mux n'active pas l'ensmeble des cannaux</t>
+  </si>
+  <si>
+    <t>0•</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Modification code de test MUX
+•Dépannage MUX (Mauvaise brassure sur résitance R7)
+•Développement firmware final pour mesure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•PV réeunion de suivit du 10,09,2025
+•Completions jorunal de travail
+•Rapport partie soft + flash firmware dans mode d'emplois. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Corrigé lecture ADC, valeur non lue correctement. 
+Verification algo, infleunce gnd , influence TVS </t>
+  </si>
+  <si>
+    <t>•Montage et test partie Buck down 5V
+•Implémentations clean de lecture de de l'adc coammnde du mux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Meeting explication API
+•Implémentations API 
+</t>
   </si>
 </sst>
 </file>
@@ -1034,11 +1090,11 @@
       </c>
       <c r="G5" s="25">
         <f>SUM(C39:I39)</f>
-        <v>0.34374999999999994</v>
+        <v>2.177083333333333</v>
       </c>
       <c r="H5" s="25">
         <f>SUM(C48:I48)</f>
-        <v>0</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="I5" s="25">
         <f>SUM(C57:I57)</f>
@@ -1046,7 +1102,7 @@
       </c>
       <c r="J5" s="25">
         <f>SUM(D5:I5)</f>
-        <v>6.677083333333333</v>
+        <v>10.177083333333332</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1228,28 +1284,28 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="212.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="283.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
@@ -1257,23 +1313,23 @@
         <v>0</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="E14" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="G14" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>25</v>
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="21" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="21" x14ac:dyDescent="0.35">
@@ -1456,28 +1512,28 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="159" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" ht="284.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
@@ -1485,11 +1541,11 @@
         <v>0</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
@@ -1680,23 +1736,23 @@
         <v>5</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="21" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1711,7 +1767,7 @@
       <c r="H32" s="21"/>
       <c r="I32" s="21"/>
     </row>
-    <row r="33" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
@@ -1721,7 +1777,7 @@
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
     </row>
-    <row r="34" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="26">
         <v>4</v>
       </c>
@@ -1754,7 +1810,7 @@
         <v>45914</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B35" s="26"/>
       <c r="C35" s="14">
         <f>I26+1</f>
@@ -1785,49 +1841,85 @@
         <v>45914</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="16">
         <v>0.34375</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-    </row>
-    <row r="37" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="D36" s="16">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="E36" s="16">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F36" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="G36" s="16">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="H36" s="16">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I36" s="16">
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="16">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-    </row>
-    <row r="38" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="D37" s="16">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E37" s="16">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F37" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="G37" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="H37" s="16">
+        <v>0.71875</v>
+      </c>
+      <c r="I37" s="16">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="17">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-    </row>
-    <row r="39" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="D38" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E38" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F38" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G38" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H38" s="17">
+        <v>0</v>
+      </c>
+      <c r="I38" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="s">
         <v>4</v>
       </c>
@@ -1837,58 +1929,79 @@
       </c>
       <c r="D39" s="19">
         <f>D37-D36-D38</f>
-        <v>0</v>
+        <v>0.36458333333333337</v>
       </c>
       <c r="E39" s="19">
         <f t="shared" ref="E39" si="19">E37-E36-E38</f>
-        <v>0</v>
+        <v>0.36458333333333337</v>
       </c>
       <c r="F39" s="19">
         <f t="shared" ref="F39" si="20">F37-F36-F38</f>
-        <v>0</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="G39" s="19">
         <f t="shared" ref="G39" si="21">G37-G36-G38</f>
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="H39" s="19">
         <f t="shared" ref="H39" si="22">H37-H36-H38</f>
-        <v>0</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="I39" s="19">
         <f t="shared" ref="I39" si="23">I37-I36-I38</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.10416666666666671</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="215.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
       <c r="B40" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-    </row>
-    <row r="41" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
+      <c r="E41" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>50</v>
+      </c>
       <c r="H41" s="21"/>
       <c r="I41" s="21"/>
     </row>
-    <row r="42" spans="2:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
       <c r="D42" s="22"/>
@@ -1898,7 +2011,7 @@
       <c r="H42" s="22"/>
       <c r="I42" s="22"/>
     </row>
-    <row r="43" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="26">
         <v>5</v>
       </c>
@@ -1931,7 +2044,7 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B44" s="26"/>
       <c r="C44" s="14">
         <f>I35+1</f>
@@ -1962,61 +2075,85 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
+      <c r="C45" s="16">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D45" s="16">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="E45" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F45" s="16">
+        <v>0.34375</v>
+      </c>
       <c r="G45" s="16"/>
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
     </row>
-    <row r="46" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
+      <c r="C46" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="D46" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="E46" s="16">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="F46" s="16">
+        <v>0.8125</v>
+      </c>
       <c r="G46" s="16"/>
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
     </row>
-    <row r="47" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
+      <c r="C47" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D47" s="17">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E47" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F47" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
     </row>
-    <row r="48" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="19">
         <f>C46-C45-C47</f>
-        <v>0</v>
+        <v>0.41666666666666663</v>
       </c>
       <c r="D48" s="19">
         <f>D46-D45-D47</f>
-        <v>0</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="E48" s="19">
         <f t="shared" ref="E48" si="29">E46-E45-E47</f>
-        <v>0</v>
+        <v>0.43749999999999994</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ref="F48" si="30">F46-F45-F47</f>
-        <v>0</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" ref="G48" si="31">G46-G45-G47</f>
@@ -2031,13 +2168,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
+      <c r="C49" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="F49" s="21"/>
       <c r="G49" s="21"/>
       <c r="H49" s="21"/>

--- a/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/JDT_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="434" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{45023EDD-0DDC-461A-BF6A-41CAE4995C50}"/>
+  <xr:revisionPtr revIDLastSave="489" documentId="8_{4277F192-9065-4C14-9BEA-4A138BE84FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A2C386A-0D6E-45F0-818B-3B3D86844245}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail hebdomadaire" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,8 @@
   <definedNames>
     <definedName name="Interval">'Journal de travail hebdomadaire'!#REF!</definedName>
     <definedName name="ScheduleStart">'Journal de travail hebdomadaire'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Journal de travail hebdomadaire'!$B$1:$I$23</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t>NOTES</t>
   </si>
@@ -77,9 +76,6 @@
   </si>
   <si>
     <t>SEMAINE 5</t>
-  </si>
-  <si>
-    <t>SEMAINE 6</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -282,8 +278,28 @@
   </si>
   <si>
     <t xml:space="preserve">•Meeting explication API
-•Implémentations API 
+•Implémentations API
+•Implémentation du calcul de sonde
+•Execution de la logiqeu de base du système 
 </t>
+  </si>
+  <si>
+    <t>•Implémentations de la page de configuration local du projet. 
+•Debug de la partie test 24[V]
+•Mesure partie stepdown
+•Réeunion de suivis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Rapport partie software
+•Avançée mode d'emplois
+</t>
+  </si>
+  <si>
+    <t>•Mesure des partie analogique alimentations
+•Rapport partie mesure</t>
+  </si>
+  <si>
+    <t>•Rapport partie finale</t>
   </si>
 </sst>
 </file>
@@ -594,13 +610,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>52918</xdr:colOff>
+      <xdr:colOff>176310</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>955416</xdr:colOff>
+      <xdr:colOff>1078808</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>608542</xdr:rowOff>
     </xdr:to>
@@ -624,7 +640,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304272" y="0"/>
+          <a:off x="438248" y="0"/>
           <a:ext cx="902498" cy="608542"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1050,7 +1066,7 @@
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>9</v>
@@ -1066,9 +1082,6 @@
       </c>
       <c r="I4" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1094,15 +1107,11 @@
       </c>
       <c r="H5" s="25">
         <f>SUM(C48:I48)</f>
-        <v>1.6666666666666665</v>
+        <v>2.822222222222222</v>
       </c>
       <c r="I5" s="25">
-        <f>SUM(C57:I57)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="25">
-        <f>SUM(D5:I5)</f>
-        <v>10.177083333333332</v>
+        <f ca="1">SUM(D5:I5)</f>
+        <v>11.332638888888887</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1289,47 +1298,47 @@
         <v>5</v>
       </c>
       <c r="C13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="E13" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="F13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="G13" s="21" t="s">
         <v>30</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>31</v>
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="E14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="F14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="G14" s="21" t="s">
         <v>19</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>20</v>
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="21" x14ac:dyDescent="0.35">
@@ -1517,23 +1526,23 @@
         <v>5</v>
       </c>
       <c r="C22" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="E22" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="F22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="G22" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>37</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
@@ -1541,11 +1550,11 @@
         <v>0</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
@@ -1736,23 +1745,23 @@
         <v>5</v>
       </c>
       <c r="C31" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="E31" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="F31" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="G31" s="21" t="s">
         <v>42</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>43</v>
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1954,31 +1963,31 @@
     </row>
     <row r="40" spans="1:9" ht="215.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="E40" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="F40" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="G40" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="G40" s="21" t="s">
-        <v>49</v>
-      </c>
       <c r="H40" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" s="21" t="s">
         <v>52</v>
-      </c>
-      <c r="I40" s="21" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1986,17 +1995,17 @@
         <v>0</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>26</v>
-      </c>
       <c r="G41" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H41" s="21"/>
       <c r="I41" s="21"/>
@@ -2091,9 +2100,15 @@
       <c r="F45" s="16">
         <v>0.34375</v>
       </c>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
+      <c r="G45" s="16">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="H45" s="16">
+        <v>0.4375</v>
+      </c>
+      <c r="I45" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
@@ -2111,9 +2126,15 @@
       <c r="F46" s="16">
         <v>0.8125</v>
       </c>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
+      <c r="G46" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="H46" s="16">
+        <v>0.99930555555555556</v>
+      </c>
+      <c r="I46" s="16">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="47" spans="1:9" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
@@ -2131,9 +2152,15 @@
       <c r="F47" s="17">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
+      <c r="G47" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H47" s="17">
+        <v>0.125</v>
+      </c>
+      <c r="I47" s="17">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="48" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="s">
@@ -2157,15 +2184,15 @@
       </c>
       <c r="G48" s="19">
         <f t="shared" ref="G48" si="31">G46-G45-G47</f>
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="H48" s="19">
         <f t="shared" ref="H48" si="32">H46-H45-H47</f>
-        <v>0</v>
+        <v>0.43680555555555556</v>
       </c>
       <c r="I48" s="19">
         <f t="shared" ref="I48" si="33">I46-I45-I47</f>
-        <v>0</v>
+        <v>0.31249999999999994</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2173,18 +2200,26 @@
         <v>5</v>
       </c>
       <c r="C49" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="E49" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="F49" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
+      <c r="G49" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="50" spans="2:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
@@ -2380,8 +2415,8 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
-  <pageSetup paperSize="3" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="26" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
